--- a/artfynd/A 19458-2024 artfynd.xlsx
+++ b/artfynd/A 19458-2024 artfynd.xlsx
@@ -3058,7 +3058,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117458398</v>
+        <v>117458827</v>
       </c>
       <c r="B25" t="n">
         <v>78480</v>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403162</v>
+        <v>403562</v>
       </c>
       <c r="R25" t="n">
-        <v>6694014</v>
+        <v>6694279</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117458539</v>
+        <v>117458657</v>
       </c>
       <c r="B26" t="n">
         <v>78480</v>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>403376</v>
+        <v>403531</v>
       </c>
       <c r="R26" t="n">
-        <v>6694176</v>
+        <v>6694235</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117458540</v>
+        <v>117458787</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>403449</v>
+        <v>403540</v>
       </c>
       <c r="R27" t="n">
-        <v>6694211</v>
+        <v>6694267</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117458450</v>
+        <v>117458786</v>
       </c>
       <c r="B29" t="n">
-        <v>57963</v>
+        <v>79596</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3498,27 +3498,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103044</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3526,13 +3525,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>403249</v>
+        <v>403540</v>
       </c>
       <c r="R29" t="n">
-        <v>6694097</v>
+        <v>6694267</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3570,6 +3569,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117458786</v>
+        <v>117458450</v>
       </c>
       <c r="B30" t="n">
-        <v>79596</v>
+        <v>57963</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3604,26 +3604,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6463</v>
+        <v>103044</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3631,13 +3632,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>403540</v>
+        <v>403249</v>
       </c>
       <c r="R30" t="n">
-        <v>6694267</v>
+        <v>6694097</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3675,7 +3676,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3694,7 +3694,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117458827</v>
+        <v>117458398</v>
       </c>
       <c r="B31" t="n">
         <v>78480</v>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403562</v>
+        <v>403162</v>
       </c>
       <c r="R31" t="n">
-        <v>6694279</v>
+        <v>6694014</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3904,14 +3904,14 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Svea Nikula, Daniel Söderström, Amanda Rudelius, Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson, Amanda Rudelius, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117458657</v>
+        <v>117458539</v>
       </c>
       <c r="B33" t="n">
         <v>78480</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403531</v>
+        <v>403376</v>
       </c>
       <c r="R33" t="n">
-        <v>6694235</v>
+        <v>6694176</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117458787</v>
+        <v>117458540</v>
       </c>
       <c r="B34" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4033,21 +4033,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>403540</v>
+        <v>403449</v>
       </c>
       <c r="R34" t="n">
-        <v>6694267</v>
+        <v>6694211</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4328,14 +4328,14 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
+          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117478637</v>
+        <v>117478679</v>
       </c>
       <c r="B37" t="n">
         <v>78480</v>
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403244</v>
+        <v>403543</v>
       </c>
       <c r="R37" t="n">
-        <v>6693987</v>
+        <v>6694133</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,17 +4434,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
+          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117478659</v>
+        <v>117478668</v>
       </c>
       <c r="B38" t="n">
-        <v>97753</v>
+        <v>97857</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,21 +4457,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403291</v>
+        <v>403421</v>
       </c>
       <c r="R38" t="n">
-        <v>6694167</v>
+        <v>6694162</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,17 +4541,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
+          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117478679</v>
+        <v>117478659</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>97753</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,30 +4560,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4591,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403543</v>
+        <v>403291</v>
       </c>
       <c r="R39" t="n">
-        <v>6694133</v>
+        <v>6694167</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4647,17 +4648,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
+          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117478668</v>
+        <v>117478637</v>
       </c>
       <c r="B40" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4666,31 +4667,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403421</v>
+        <v>403244</v>
       </c>
       <c r="R40" t="n">
-        <v>6694162</v>
+        <v>6693987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 19458-2024 artfynd.xlsx
+++ b/artfynd/A 19458-2024 artfynd.xlsx
@@ -3058,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117458827</v>
+        <v>117458657</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403562</v>
+        <v>403531</v>
       </c>
       <c r="R25" t="n">
-        <v>6694279</v>
+        <v>6694235</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3164,10 +3164,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117458657</v>
+        <v>117458398</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>403531</v>
+        <v>403162</v>
       </c>
       <c r="R26" t="n">
-        <v>6694235</v>
+        <v>6694014</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117458787</v>
+        <v>117458539</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>403540</v>
+        <v>403376</v>
       </c>
       <c r="R27" t="n">
-        <v>6694267</v>
+        <v>6694176</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3376,10 +3376,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117458536</v>
+        <v>117458787</v>
       </c>
       <c r="B28" t="n">
-        <v>90517</v>
+        <v>79563</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3392,21 +3392,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>403343</v>
+        <v>403540</v>
       </c>
       <c r="R28" t="n">
-        <v>6694132</v>
+        <v>6694267</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117458786</v>
+        <v>117458827</v>
       </c>
       <c r="B29" t="n">
-        <v>79596</v>
+        <v>78482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3494,20 +3494,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3525,10 +3525,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>403540</v>
+        <v>403562</v>
       </c>
       <c r="R29" t="n">
-        <v>6694267</v>
+        <v>6694279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117458450</v>
+        <v>117458536</v>
       </c>
       <c r="B30" t="n">
-        <v>57963</v>
+        <v>90519</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3600,31 +3600,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103044</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3632,13 +3631,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>403249</v>
+        <v>403343</v>
       </c>
       <c r="R30" t="n">
-        <v>6694097</v>
+        <v>6694132</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3676,6 +3675,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117458398</v>
+        <v>117458540</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403162</v>
+        <v>403449</v>
       </c>
       <c r="R31" t="n">
-        <v>6694014</v>
+        <v>6694211</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3803,7 +3803,7 @@
         <v>117458411</v>
       </c>
       <c r="B32" t="n">
-        <v>74584</v>
+        <v>74586</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117458539</v>
+        <v>117458450</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>57964</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3923,30 +3923,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103044</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3954,13 +3955,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403376</v>
+        <v>403249</v>
       </c>
       <c r="R33" t="n">
-        <v>6694176</v>
+        <v>6694097</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3998,7 +3999,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4017,10 +4017,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117458540</v>
+        <v>117458786</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>79598</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4029,20 +4029,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>403449</v>
+        <v>403540</v>
       </c>
       <c r="R34" t="n">
-        <v>6694211</v>
+        <v>6694267</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117478645</v>
+        <v>117478659</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>97755</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4135,30 +4135,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4166,10 +4167,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>403260</v>
+        <v>403291</v>
       </c>
       <c r="R35" t="n">
-        <v>6694029</v>
+        <v>6694167</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4229,10 +4230,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117478647</v>
+        <v>117478637</v>
       </c>
       <c r="B36" t="n">
-        <v>82259</v>
+        <v>78482</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4245,21 +4246,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4272,10 +4273,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403260</v>
+        <v>403244</v>
       </c>
       <c r="R36" t="n">
-        <v>6694029</v>
+        <v>6693987</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4328,17 +4329,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117478679</v>
+        <v>117478668</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>97859</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4347,30 +4348,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4378,10 +4380,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403543</v>
+        <v>403421</v>
       </c>
       <c r="R37" t="n">
-        <v>6694133</v>
+        <v>6694162</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,17 +4436,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117478668</v>
+        <v>117478679</v>
       </c>
       <c r="B38" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4453,31 +4455,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4485,10 +4486,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>403421</v>
+        <v>403543</v>
       </c>
       <c r="R38" t="n">
-        <v>6694162</v>
+        <v>6694133</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,17 +4542,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117478659</v>
+        <v>117478645</v>
       </c>
       <c r="B39" t="n">
-        <v>97753</v>
+        <v>78482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4560,31 +4561,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>403291</v>
+        <v>403260</v>
       </c>
       <c r="R39" t="n">
-        <v>6694167</v>
+        <v>6694029</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,17 +4648,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Svea Nikula, Daniel Söderström, August Oljeqvist, Amanda Rudelius, Jonas Göransson</t>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Daniel Söderström, Svea Nikula</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117478637</v>
+        <v>117478647</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>82261</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>403244</v>
+        <v>403260</v>
       </c>
       <c r="R40" t="n">
-        <v>6693987</v>
+        <v>6694029</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4764,7 @@
         <v>117566807</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>117566835</v>
       </c>
       <c r="B42" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
